--- a/Excel/WorldConfig.xlsx
+++ b/Excel/WorldConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>极朱雀</t>
+  </si>
+  <si>
+    <t>极玄武</t>
   </si>
 </sst>
 </file>
@@ -86,7 +89,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,7 +102,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -107,25 +109,11 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+    </font>
+    <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF333333"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -597,148 +585,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1092,10 +1076,10 @@
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="3"/>
@@ -1108,10 +1092,10 @@
       <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="3"/>
@@ -1124,10 +1108,10 @@
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="3"/>
@@ -1135,46 +1119,46 @@
       <c r="H5" s="2"/>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="1:8">
-      <c r="C6" s="5">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
-      <c r="C7" s="5">
+      <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="1">
         <v>6</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
-      <c r="C8" s="5">
+      <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
-      <c r="C9" s="5">
+      <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>10</v>
       </c>
     </row>
@@ -1222,7 +1206,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1"/>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1">
+        <v>29</v>
+      </c>
+    </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
     <row r="17" s="1" customFormat="1" customHeight="1"/>
